--- a/APPENDIX/additional_experiments/hydronewsfr_extended_chronological_eval_k440.xlsx
+++ b/APPENDIX/additional_experiments/hydronewsfr_extended_chronological_eval_k440.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/evangeliazve/Documents/Papier EMNLP/Dossier Github - supp material/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E94F700A-749A-0743-A0D9-69140F44A9CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3501FF2-8764-1D41-8226-34946836D0E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2140" yWindow="3680" windowWidth="29400" windowHeight="17040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="29400" windowHeight="17040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="32">
-  <si>
-    <t>scenario</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
     <t>horizon</t>
   </si>
@@ -97,35 +94,30 @@
     <t>Recall</t>
   </si>
   <si>
-    <t>chronological_date_exclusive</t>
-  </si>
-  <si>
     <t>TA</t>
   </si>
   <si>
     <t>baseline_all_pos</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>baseline_all_neg</t>
-  </si>
-  <si>
     <t>all_features</t>
   </si>
   <si>
     <t>xgb</t>
+  </si>
+  <si>
+    <t>baseline</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -135,17 +127,31 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="14"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -175,10 +181,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
@@ -483,321 +501,246 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y4"/>
+  <dimension ref="A1:X3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="22.6640625" customWidth="1"/>
-    <col min="20" max="20" width="17.6640625" customWidth="1"/>
+    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="20.83203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.83203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.1640625" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:24" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="W1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" ht="19" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="X1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>21</v>
+      <c r="B2" s="1">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="F2" s="2">
+        <v>45758</v>
+      </c>
+      <c r="G2" s="1">
+        <v>656</v>
+      </c>
+      <c r="H2" s="1">
+        <v>323</v>
+      </c>
+      <c r="I2" s="1">
+        <v>333</v>
+      </c>
+      <c r="J2" s="1">
+        <v>224</v>
+      </c>
+      <c r="K2" s="1">
+        <v>99</v>
+      </c>
+      <c r="L2" s="1">
+        <v>16</v>
+      </c>
+      <c r="M2" s="1">
+        <v>317</v>
+      </c>
+      <c r="N2" s="2">
+        <v>45663</v>
+      </c>
+      <c r="O2" s="2">
+        <v>45757</v>
+      </c>
+      <c r="P2" s="2">
+        <v>45758</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>45816</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="T2" s="5">
+        <v>9.1690544412607447E-2</v>
+      </c>
+      <c r="U2" s="5">
+        <v>4.8048048048048048E-2</v>
+      </c>
+      <c r="V2" s="5">
+        <v>1</v>
+      </c>
+      <c r="W2" s="5">
+        <v>4.8048048048048048E-2</v>
+      </c>
+      <c r="X2" s="5">
+        <v>0.5</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="3" spans="1:24" ht="19" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="1">
+        <v>4</v>
+      </c>
+      <c r="C3" s="1">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="F3" s="2">
+        <v>45758</v>
+      </c>
+      <c r="G3" s="1">
+        <v>656</v>
+      </c>
+      <c r="H3" s="1">
+        <v>323</v>
+      </c>
+      <c r="I3" s="1">
+        <v>333</v>
+      </c>
+      <c r="J3" s="1">
+        <v>224</v>
+      </c>
+      <c r="K3" s="1">
+        <v>99</v>
+      </c>
+      <c r="L3" s="1">
+        <v>16</v>
+      </c>
+      <c r="M3" s="1">
+        <v>317</v>
+      </c>
+      <c r="N3" s="2">
+        <v>45663</v>
+      </c>
+      <c r="O3" s="2">
+        <v>45757</v>
+      </c>
+      <c r="P3" s="2">
+        <v>45758</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>45816</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="S3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>4</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0.5</v>
-      </c>
-      <c r="G2" s="2">
-        <v>45758</v>
-      </c>
-      <c r="H2">
-        <v>656</v>
-      </c>
-      <c r="I2">
-        <v>323</v>
-      </c>
-      <c r="J2">
-        <v>333</v>
-      </c>
-      <c r="K2">
-        <v>224</v>
-      </c>
-      <c r="L2">
-        <v>99</v>
-      </c>
-      <c r="M2">
-        <v>16</v>
-      </c>
-      <c r="N2">
-        <v>317</v>
-      </c>
-      <c r="O2" s="2">
-        <v>45663</v>
-      </c>
-      <c r="P2" s="2">
-        <v>45757</v>
-      </c>
-      <c r="Q2" s="2">
-        <v>45758</v>
-      </c>
-      <c r="R2" s="2">
-        <v>45816</v>
-      </c>
-      <c r="S2" t="s">
-        <v>27</v>
-      </c>
-      <c r="T2" t="s">
-        <v>28</v>
-      </c>
-      <c r="U2">
-        <v>9.1690544412607447E-2</v>
-      </c>
-      <c r="V2">
-        <v>4.8048048048048048E-2</v>
-      </c>
-      <c r="W2">
-        <v>1</v>
-      </c>
-      <c r="X2">
-        <v>4.8048048048048048E-2</v>
-      </c>
-      <c r="Y2">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0.5</v>
-      </c>
-      <c r="G3" s="2">
-        <v>45758</v>
-      </c>
-      <c r="H3">
-        <v>656</v>
-      </c>
-      <c r="I3">
-        <v>323</v>
-      </c>
-      <c r="J3">
-        <v>333</v>
-      </c>
-      <c r="K3">
-        <v>224</v>
-      </c>
-      <c r="L3">
-        <v>99</v>
-      </c>
-      <c r="M3">
-        <v>16</v>
-      </c>
-      <c r="N3">
-        <v>317</v>
-      </c>
-      <c r="O3" s="2">
-        <v>45663</v>
-      </c>
-      <c r="P3" s="2">
-        <v>45757</v>
-      </c>
-      <c r="Q3" s="2">
-        <v>45758</v>
-      </c>
-      <c r="R3" s="2">
-        <v>45816</v>
-      </c>
-      <c r="S3" t="s">
-        <v>29</v>
-      </c>
-      <c r="T3" t="s">
-        <v>28</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3">
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <v>4.8048048048048048E-2</v>
-      </c>
-      <c r="Y3">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-      <c r="D4">
-        <v>4</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0.5</v>
-      </c>
-      <c r="G4" s="2">
-        <v>45758</v>
-      </c>
-      <c r="H4">
-        <v>656</v>
-      </c>
-      <c r="I4">
-        <v>323</v>
-      </c>
-      <c r="J4">
-        <v>333</v>
-      </c>
-      <c r="K4">
-        <v>224</v>
-      </c>
-      <c r="L4">
-        <v>99</v>
-      </c>
-      <c r="M4">
-        <v>16</v>
-      </c>
-      <c r="N4">
-        <v>317</v>
-      </c>
-      <c r="O4" s="2">
-        <v>45663</v>
-      </c>
-      <c r="P4" s="2">
-        <v>45757</v>
-      </c>
-      <c r="Q4" s="2">
-        <v>45758</v>
-      </c>
-      <c r="R4" s="2">
-        <v>45816</v>
-      </c>
-      <c r="S4" t="s">
-        <v>31</v>
-      </c>
-      <c r="T4" t="s">
-        <v>30</v>
-      </c>
-      <c r="U4">
+      <c r="T3" s="5">
         <v>0.8</v>
       </c>
-      <c r="V4">
+      <c r="U3" s="5">
         <v>0.73684210526315785</v>
       </c>
-      <c r="W4">
+      <c r="V3" s="5">
         <v>0.875</v>
       </c>
-      <c r="X4">
+      <c r="W3" s="5">
         <v>0.76429662716669289</v>
       </c>
-      <c r="Y4">
+      <c r="X3" s="5">
         <v>0.97436908517350151</v>
       </c>
     </row>
